--- a/tools/importer/reports/import-cards-showcase.report.xlsx
+++ b/tools/importer/reports/import-cards-showcase.report.xlsx
@@ -94,7 +94,7 @@
     <t>cards-showcase</t>
   </si>
   <si>
-    <t>2026-08-30T17:08:50.292Z</t>
+    <t>2026-08-30T19:03:54.003Z</t>
   </si>
   <si>
     <t>Fashion Trends for Young Adults | Fashion Blog</t>
